--- a/backend/data/别墅装修_最新.xlsx
+++ b/backend/data/别墅装修_最新.xlsx
@@ -1813,7 +1813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG55"/>
+  <dimension ref="A1:AJ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="184" min="1" max="1"/>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="M8" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="N8" s="47" t="inlineStr">
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>

--- a/backend/data/别墅装修_最新.xlsx
+++ b/backend/data/别墅装修_最新.xlsx
@@ -2288,7 +2288,7 @@
       </c>
       <c r="M8" s="46" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="N8" s="47" t="inlineStr">
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="M27" s="46" t="inlineStr">
         <is>
-          <t>已下单</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="N27" s="47" t="inlineStr">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>

--- a/backend/data/别墅装修_最新.xlsx
+++ b/backend/data/别墅装修_最新.xlsx
@@ -3018,7 +3018,7 @@
       </c>
       <c r="M18" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="N18" s="47" t="inlineStr">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>

--- a/backend/data/别墅装修_最新.xlsx
+++ b/backend/data/别墅装修_最新.xlsx
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M20" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="N20" s="47" t="inlineStr">
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>

--- a/backend/data/别墅装修_最新.xlsx
+++ b/backend/data/别墅装修_最新.xlsx
@@ -3018,7 +3018,7 @@
       </c>
       <c r="M18" s="46" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="N18" s="47" t="inlineStr">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -3178,7 +3178,11 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="42" customHeight="1" s="184">
       <c r="A21" s="43" t="inlineStr">

--- a/backend/data/别墅装修_最新.xlsx
+++ b/backend/data/别墅装修_最新.xlsx
@@ -3018,7 +3018,7 @@
       </c>
       <c r="M18" s="46" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已支付</t>
         </is>
       </c>
       <c r="N18" s="47" t="inlineStr">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>

--- a/backend/data/别墅装修_最新.xlsx
+++ b/backend/data/别墅装修_最新.xlsx
@@ -3018,7 +3018,7 @@
       </c>
       <c r="M18" s="46" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="N18" s="47" t="inlineStr">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M20" s="46" t="inlineStr">
         <is>
-          <t>已支付</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="N20" s="47" t="inlineStr">
@@ -3173,16 +3173,12 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>待补充</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21" ht="42" customHeight="1" s="184">
       <c r="A21" s="43" t="inlineStr">
